--- a/examples/excel/pivot-tables.xlsx
+++ b/examples/excel/pivot-tables.xlsx
@@ -3,31 +3,31 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="CNData" sheetId="2" r:id="Rfa2f4f1d8a56428d"/>
-    <x:sheet name="1-Sales Overview" sheetId="3" r:id="R1ab5d031d8f84159"/>
-    <x:sheet name="2-Market Share" sheetId="4" r:id="Rb52fc8ce73dc4b66"/>
-    <x:sheet name="3-Product Deep Dive" sheetId="5" r:id="Rc043ebb0a3e54231"/>
-    <x:sheet name="4-Channel Analysis" sheetId="6" r:id="R4b8ff493cb3f4154"/>
-    <x:sheet name="5-Priority Matrix" sheetId="7" r:id="Rc261dafdada343e9"/>
-    <x:sheet name="6-Compact 3-Level" sheetId="8" r:id="Rb84b37ac538741d3"/>
-    <x:sheet name="7-No Subtotals" sheetId="9" r:id="R5c3ec716001d4370"/>
-    <x:sheet name="8-Date Grouping" sheetId="10" r:id="Rf5831a060b704b09"/>
-    <x:sheet name="9-Top 5 Products" sheetId="11" r:id="R0a2288c10d9d4908"/>
-    <x:sheet name="10-Ultimate" sheetId="12" r:id="R87396368a8064634"/>
-    <x:sheet name="11-Chinese Locale" sheetId="13" r:id="R8d6ba6f71d664f20"/>
-    <x:sheet name="12-Position + Aggregates" sheetId="14" r:id="R3c272421b0634f62"/>
-    <x:sheet name="13-Calculated Field" sheetId="15" r:id="R7ca93a1ef796497a"/>
-    <x:sheet name="14-Statistical" sheetId="16" r:id="R2dfdc0b142454b90"/>
-    <x:sheet name="15-Independent Totals" sheetId="17" r:id="R43506f9449794503"/>
-    <x:sheet name="16-Style Flags" sheetId="18" r:id="R12f2a17d002f4a34"/>
-    <x:sheet name="17-Display Toggles" sheetId="19" r:id="R298b36fe782a4cfa"/>
+    <x:sheet name="CNData" sheetId="2" r:id="Refcc286486c14d76"/>
+    <x:sheet name="1-Sales Overview" sheetId="3" r:id="R8a3a3f5e138349a2"/>
+    <x:sheet name="2-Market Share" sheetId="4" r:id="Rcf86d0c793e24249"/>
+    <x:sheet name="3-Product Deep Dive" sheetId="5" r:id="R09b9c10595fb4280"/>
+    <x:sheet name="4-Channel Analysis" sheetId="6" r:id="R3de07eb138be4abd"/>
+    <x:sheet name="5-Priority Matrix" sheetId="7" r:id="R7c968571955d4cd1"/>
+    <x:sheet name="6-Compact 3-Level" sheetId="8" r:id="R7668433898d34189"/>
+    <x:sheet name="7-No Subtotals" sheetId="9" r:id="Rc75fa42f28904d96"/>
+    <x:sheet name="8-Date Grouping" sheetId="10" r:id="R5bf5e56701654ae5"/>
+    <x:sheet name="9-Top 5 Products" sheetId="11" r:id="R8b99fac75eb24cbc"/>
+    <x:sheet name="10-Ultimate" sheetId="12" r:id="R6f32aae80b8b477c"/>
+    <x:sheet name="11-Chinese Locale" sheetId="13" r:id="R35370318ebc04481"/>
+    <x:sheet name="12-Position + Aggregates" sheetId="14" r:id="R9e30584ebca84f9a"/>
+    <x:sheet name="13-Calculated Field" sheetId="15" r:id="R5f3660bcfdd9456b"/>
+    <x:sheet name="14-Statistical" sheetId="16" r:id="Red08d58ad03c4f97"/>
+    <x:sheet name="15-Independent Totals" sheetId="17" r:id="R254fba06e4a44127"/>
+    <x:sheet name="16-Style Flags" sheetId="18" r:id="R3d5f4fb298a743c9"/>
+    <x:sheet name="17-Display Toggles" sheetId="19" r:id="R7f023e90939841b0"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache cacheId="0" r:id="Rf0fa8c9e10a94fb4"/>
-    <x:pivotCache cacheId="1" r:id="R4fb92e772a6c4cbf"/>
-    <x:pivotCache cacheId="2" r:id="R22a83956b2354de0"/>
-    <x:pivotCache cacheId="3" r:id="R5e88c575d0e34143"/>
-    <x:pivotCache cacheId="4" r:id="R8a40d7bbe87742a4"/>
+    <x:pivotCache cacheId="0" r:id="R83bd7747752d4f2f"/>
+    <x:pivotCache cacheId="1" r:id="Re961fe03044a4e98"/>
+    <x:pivotCache cacheId="2" r:id="R7c1e5f03ef754a0b"/>
+    <x:pivotCache cacheId="3" r:id="R11cce27e084b4045"/>
+    <x:pivotCache cacheId="4" r:id="R5e82873f3b8b42c3"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
@@ -2064,6 +2064,115 @@
 </x:pivotTableDefinition>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
@@ -10074,7 +10183,7 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="Red8fb75acfd44546" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="Re8f08e18e1184783" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
   </x:cacheSource>
@@ -10145,7 +10254,7 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R4f7a4f28d64d4901" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R2a37173c98a64369" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
   </x:cacheSource>
@@ -10292,7 +10401,7 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R237c8f12fa054355" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="29">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R316daea1745e4442" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="29">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
   </x:cacheSource>
@@ -10358,7 +10467,7 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R341dfe75eff34ca9" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="12">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R9e0d0f44319e4afe" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="12">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:C13" sheet="CNData"/>
   </x:cacheSource>
@@ -10386,7 +10495,7 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R6b0d5e0431424bc7" refreshOnLoad="1" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R7a1f1b996e564364" refreshOnLoad="1" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
   </x:cacheSource>
